--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mator\OneDrive\ドキュメント\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64868D8B-1F05-445E-BB4C-3505C2CE11AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B6C286C-DDD1-4C2D-B262-D384B7AF0DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3660" yWindow="1005" windowWidth="21915" windowHeight="13455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3240" yWindow="2115" windowWidth="23295" windowHeight="13305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -13635,16 +13635,16 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>50</v>
-      </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
-      <c r="M70" s="3">
-        <v>0</v>
       </c>
       <c r="N70" s="3">
         <v>0</v>
